--- a/Экономика/ЛР2.xlsx
+++ b/Экономика/ЛР2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\labs\labs-6-sem\Экономика\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F558C4-1ABD-4DB3-B739-097C4ED0F391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B738079A-A1F9-40AB-B538-D5FED66BBF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="97">
   <si>
     <t>Таблица 1. Баланс рабочего времени одного среднесписочного рабочего</t>
   </si>
@@ -412,23 +412,35 @@
   <si>
     <t>ЗА ЧАС ПЕРЕВЕСТИ ИЗ МЕСЯЦА - 520</t>
   </si>
+  <si>
+    <t>?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -647,291 +659,297 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1232,80 +1250,80 @@
     <col min="42" max="42" width="15.33203125" customWidth="1"/>
     <col min="44" max="44" width="8.88671875" customWidth="1"/>
     <col min="47" max="47" width="53.33203125" customWidth="1"/>
-    <col min="48" max="48" width="26.6640625" customWidth="1"/>
+    <col min="48" max="48" width="30.109375" customWidth="1"/>
     <col min="49" max="49" width="24.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="11"/>
-      <c r="N1" s="15" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
     </row>
     <row r="2" spans="1:49" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
-      <c r="N2" s="18" t="s">
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="89"/>
+      <c r="N2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="14"/>
-      <c r="AA2" s="15" t="s">
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
+      <c r="W2" s="88"/>
+      <c r="X2" s="89"/>
+      <c r="AA2" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="38"/>
+      <c r="AB2" s="96"/>
+      <c r="AC2" s="96"/>
+      <c r="AD2" s="96"/>
+      <c r="AE2" s="96"/>
+      <c r="AF2" s="96"/>
+      <c r="AG2" s="96"/>
+      <c r="AH2" s="96"/>
+      <c r="AI2" s="30"/>
     </row>
     <row r="3" spans="1:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -1321,54 +1339,54 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="33">
+      <c r="N3" s="11"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="26">
         <v>2</v>
       </c>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
-      <c r="AA3" s="39" t="s">
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="AA3" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="AB3" s="40">
+      <c r="AB3" s="32">
         <v>1</v>
       </c>
-      <c r="AC3" s="40">
+      <c r="AC3" s="32">
         <v>2</v>
       </c>
-      <c r="AD3" s="40">
+      <c r="AD3" s="32">
         <v>3</v>
       </c>
-      <c r="AE3" s="40">
+      <c r="AE3" s="32">
         <v>4</v>
       </c>
-      <c r="AF3" s="40">
+      <c r="AF3" s="32">
         <v>5</v>
       </c>
-      <c r="AG3" s="40">
+      <c r="AG3" s="32">
         <v>6</v>
       </c>
-      <c r="AH3" s="40">
+      <c r="AH3" s="32">
         <v>7</v>
       </c>
-      <c r="AI3" s="41">
+      <c r="AI3" s="33">
         <v>8</v>
       </c>
-      <c r="AM3" s="66" t="s">
+      <c r="AM3" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="AN3" s="66"/>
-      <c r="AO3" s="66"/>
-      <c r="AP3" s="66"/>
-      <c r="AQ3" s="67"/>
-      <c r="AR3" s="67"/>
+      <c r="AN3" s="90"/>
+      <c r="AO3" s="90"/>
+      <c r="AP3" s="90"/>
+      <c r="AQ3" s="56"/>
+      <c r="AR3" s="56"/>
     </row>
     <row r="4" spans="1:49" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1386,66 +1404,66 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="N4" s="17" t="s">
+      <c r="N4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19">
+      <c r="O4" s="12"/>
+      <c r="P4" s="12">
         <v>520</v>
       </c>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="AA4" s="39" t="s">
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="AA4" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="AB4" s="44">
-        <f>$P$4*AB5</f>
-        <v>520</v>
-      </c>
-      <c r="AC4" s="44">
-        <f>$P$4*AC5</f>
-        <v>603.19999999999993</v>
-      </c>
-      <c r="AD4" s="44">
-        <f t="shared" ref="AD4:AH4" si="0">$P$4*AD5</f>
-        <v>702</v>
-      </c>
-      <c r="AE4" s="44">
+      <c r="AB4" s="36">
+        <f>($P$4*12/$C$13)*AB5</f>
+        <v>3.5294117647058822</v>
+      </c>
+      <c r="AC4" s="36">
+        <f t="shared" ref="AC4:AI4" si="0">($P$4*12/$C$13)*AC5</f>
+        <v>4.0941176470588232</v>
+      </c>
+      <c r="AD4" s="36">
         <f t="shared" si="0"/>
-        <v>816.4</v>
-      </c>
-      <c r="AF4" s="44">
+        <v>4.7647058823529411</v>
+      </c>
+      <c r="AE4" s="36">
         <f t="shared" si="0"/>
-        <v>899.6</v>
-      </c>
-      <c r="AG4" s="44">
+        <v>5.5411764705882351</v>
+      </c>
+      <c r="AF4" s="36">
         <f t="shared" si="0"/>
-        <v>988</v>
-      </c>
-      <c r="AH4" s="44">
+        <v>6.1058823529411761</v>
+      </c>
+      <c r="AG4" s="36">
         <f t="shared" si="0"/>
-        <v>1055.5999999999999</v>
-      </c>
-      <c r="AI4" s="44">
-        <f>$P$4*AI5</f>
-        <v>1128.3999999999999</v>
-      </c>
-      <c r="AM4" s="63" t="s">
+        <v>6.7058823529411757</v>
+      </c>
+      <c r="AH4" s="36">
+        <f t="shared" si="0"/>
+        <v>7.1647058823529406</v>
+      </c>
+      <c r="AI4" s="36">
+        <f t="shared" si="0"/>
+        <v>7.6588235294117641</v>
+      </c>
+      <c r="AM4" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="AN4" s="12" t="s">
+      <c r="AN4" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="AO4" s="13"/>
-      <c r="AP4" s="14"/>
-      <c r="AQ4" s="72"/>
-      <c r="AR4" s="72"/>
+      <c r="AO4" s="88"/>
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="61"/>
+      <c r="AR4" s="61"/>
     </row>
     <row r="5" spans="1:49" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1463,65 +1481,65 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="N5" s="17" t="s">
+      <c r="N5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19">
+      <c r="O5" s="12"/>
+      <c r="P5" s="12">
         <v>55</v>
       </c>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
-      <c r="AA5" s="39" t="s">
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="AA5" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="AB5" s="42">
+      <c r="AB5" s="34">
         <v>1</v>
       </c>
-      <c r="AC5" s="43">
+      <c r="AC5" s="35">
         <v>1.1599999999999999</v>
       </c>
-      <c r="AD5" s="43">
+      <c r="AD5" s="35">
         <v>1.35</v>
       </c>
-      <c r="AE5" s="43">
+      <c r="AE5" s="35">
         <v>1.57</v>
       </c>
-      <c r="AF5" s="43">
+      <c r="AF5" s="35">
         <v>1.73</v>
       </c>
-      <c r="AG5" s="43">
+      <c r="AG5" s="35">
         <v>1.9</v>
       </c>
-      <c r="AH5" s="43">
+      <c r="AH5" s="35">
         <v>2.0299999999999998</v>
       </c>
-      <c r="AI5" s="43">
+      <c r="AI5" s="35">
         <v>2.17</v>
       </c>
-      <c r="AM5" s="63"/>
-      <c r="AN5" s="70" t="s">
+      <c r="AM5" s="86"/>
+      <c r="AN5" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="AO5" s="70" t="s">
+      <c r="AO5" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="AP5" s="70" t="s">
+      <c r="AP5" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="AQ5" s="73"/>
-      <c r="AR5" s="74"/>
-      <c r="AU5" s="92" t="s">
+      <c r="AQ5" s="62"/>
+      <c r="AR5" s="63"/>
+      <c r="AU5" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="AV5" s="90"/>
-      <c r="AW5" s="90"/>
+      <c r="AV5" s="77"/>
+      <c r="AW5" s="77"/>
     </row>
     <row r="6" spans="1:49" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1540,48 +1558,48 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="N6" s="17" t="s">
+      <c r="N6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19">
+      <c r="O6" s="12"/>
+      <c r="P6" s="12">
         <v>3</v>
       </c>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="AA6" s="96" t="s">
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="AA6" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="AM6" s="69" t="s">
+      <c r="AM6" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="AN6" s="71">
+      <c r="AN6" s="60">
         <f>AG14</f>
-        <v>3733672.8</v>
-      </c>
-      <c r="AO6" s="71">
+        <v>101473.83529411764</v>
+      </c>
+      <c r="AO6" s="60">
         <f>AG18</f>
-        <v>2182580.4</v>
-      </c>
-      <c r="AP6" s="71">
+        <v>14813.894117647058</v>
+      </c>
+      <c r="AP6" s="60">
         <f>AG22</f>
-        <v>1373486.4</v>
-      </c>
-      <c r="AQ6" s="73"/>
-      <c r="AR6" s="68"/>
-      <c r="AU6" s="93" t="s">
+        <v>9322.3058823529391</v>
+      </c>
+      <c r="AQ6" s="62"/>
+      <c r="AR6" s="57"/>
+      <c r="AU6" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="AV6" s="91" t="s">
+      <c r="AV6" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="AW6" s="90"/>
+      <c r="AW6" s="77"/>
     </row>
     <row r="7" spans="1:49" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1600,57 +1618,57 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
-      <c r="N7" s="17" t="s">
+      <c r="N7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19">
+      <c r="O7" s="12"/>
+      <c r="P7" s="12">
         <v>15960</v>
       </c>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
-      <c r="AA7" s="37" t="s">
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="AA7" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="37"/>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="37"/>
-      <c r="AF7" s="37"/>
-      <c r="AG7" s="37"/>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="37"/>
-      <c r="AM7" s="69" t="s">
+      <c r="AB7" s="84"/>
+      <c r="AC7" s="84"/>
+      <c r="AD7" s="84"/>
+      <c r="AE7" s="84"/>
+      <c r="AF7" s="84"/>
+      <c r="AG7" s="84"/>
+      <c r="AH7" s="84"/>
+      <c r="AI7" s="84"/>
+      <c r="AM7" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="AN7" s="71">
+      <c r="AN7" s="60">
         <f>AN6*P5/100</f>
-        <v>2053520.04</v>
-      </c>
-      <c r="AO7" s="71">
+        <v>55810.609411764701</v>
+      </c>
+      <c r="AO7" s="60">
         <f>AO6*P5/100</f>
-        <v>1200419.22</v>
-      </c>
-      <c r="AP7" s="71">
+        <v>8147.6417647058815</v>
+      </c>
+      <c r="AP7" s="60">
         <f>AP6*P5/100</f>
-        <v>755417.52</v>
-      </c>
-      <c r="AQ7" s="73"/>
-      <c r="AR7" s="68"/>
-      <c r="AU7" s="93" t="s">
+        <v>5127.2682352941165</v>
+      </c>
+      <c r="AQ7" s="62"/>
+      <c r="AR7" s="57"/>
+      <c r="AU7" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="AV7" s="94">
+      <c r="AV7" s="81">
         <f>SUM(AN13:AP13)+SUM(AS21)</f>
-        <v>13914142.542986423</v>
-      </c>
-      <c r="AW7" s="90"/>
+        <v>633402.41562416824</v>
+      </c>
+      <c r="AW7" s="77"/>
     </row>
     <row r="8" spans="1:49" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
@@ -1668,56 +1686,56 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-      <c r="N8" s="20" t="s">
+      <c r="N8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="21"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="AA8" s="63" t="s">
+      <c r="O8" s="14"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="AA8" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="AB8" s="63" t="s">
+      <c r="AB8" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="AC8" s="63"/>
-      <c r="AD8" s="63"/>
-      <c r="AE8" s="63"/>
-      <c r="AF8" s="63" t="s">
+      <c r="AC8" s="86"/>
+      <c r="AD8" s="86"/>
+      <c r="AE8" s="86"/>
+      <c r="AF8" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="AG8" s="63"/>
-      <c r="AH8" s="51"/>
-      <c r="AI8" s="51"/>
-      <c r="AM8" s="69" t="s">
+      <c r="AG8" s="86"/>
+      <c r="AH8" s="43"/>
+      <c r="AI8" s="43"/>
+      <c r="AM8" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="AN8" s="80" t="s">
+      <c r="AN8" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="AO8" s="80" t="s">
+      <c r="AO8" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="AP8" s="80" t="s">
+      <c r="AP8" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="AQ8" s="78"/>
-      <c r="AR8" s="79"/>
-      <c r="AU8" s="93" t="s">
+      <c r="AQ8" s="91"/>
+      <c r="AR8" s="92"/>
+      <c r="AU8" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="AV8" s="94">
-        <f>AN21+3</f>
-        <v>10</v>
-      </c>
-      <c r="AW8" s="90"/>
+      <c r="AV8" s="81">
+        <f>AN21+AE23+3</f>
+        <v>40.909502262443439</v>
+      </c>
+      <c r="AW8" s="77"/>
     </row>
     <row r="9" spans="1:49" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
@@ -1735,63 +1753,63 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="N9" s="23" t="s">
+      <c r="N9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="24"/>
-      <c r="P9" s="25">
+      <c r="O9" s="17"/>
+      <c r="P9" s="18">
         <v>2</v>
       </c>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="AA9" s="63"/>
-      <c r="AB9" s="64" t="s">
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
+      <c r="AA9" s="86"/>
+      <c r="AB9" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="AC9" s="63" t="s">
+      <c r="AC9" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="AD9" s="63"/>
-      <c r="AE9" s="64" t="s">
+      <c r="AD9" s="86"/>
+      <c r="AE9" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="AF9" s="63" t="s">
+      <c r="AF9" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="AG9" s="63" t="s">
+      <c r="AG9" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="AH9" s="51"/>
-      <c r="AI9" s="51"/>
-      <c r="AM9" s="69" t="s">
+      <c r="AH9" s="43"/>
+      <c r="AI9" s="43"/>
+      <c r="AM9" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="AN9" s="71">
+      <c r="AN9" s="60">
         <f>AN6/P6*40/100</f>
-        <v>497823.03999999992</v>
-      </c>
-      <c r="AO9" s="71">
+        <v>13529.844705882351</v>
+      </c>
+      <c r="AO9" s="60">
         <f>AO6/P6*40/100</f>
-        <v>291010.71999999997</v>
-      </c>
-      <c r="AP9" s="71">
+        <v>1975.1858823529412</v>
+      </c>
+      <c r="AP9" s="60">
         <f>AP6/P6*40/100</f>
-        <v>183131.51999999999</v>
-      </c>
-      <c r="AQ9" s="78"/>
-      <c r="AR9" s="79"/>
-      <c r="AU9" s="93" t="s">
+        <v>1242.9741176470584</v>
+      </c>
+      <c r="AQ9" s="91"/>
+      <c r="AR9" s="92"/>
+      <c r="AU9" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="AV9" s="95">
+      <c r="AV9" s="82">
         <f>AV7/AV8</f>
-        <v>1391414.2542986423</v>
+        <v>15483.014473281846</v>
       </c>
     </row>
     <row r="10" spans="1:49" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -1810,57 +1828,57 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-      <c r="N10" s="23" t="s">
+      <c r="N10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="24"/>
-      <c r="P10" s="25">
+      <c r="O10" s="17"/>
+      <c r="P10" s="18">
         <v>4</v>
       </c>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="AA10" s="63"/>
-      <c r="AB10" s="64"/>
-      <c r="AC10" s="62" t="s">
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="AA10" s="86"/>
+      <c r="AB10" s="85"/>
+      <c r="AC10" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="AD10" s="62" t="s">
+      <c r="AD10" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="AE10" s="64"/>
-      <c r="AF10" s="63"/>
-      <c r="AG10" s="63"/>
-      <c r="AH10" s="51"/>
-      <c r="AI10" s="51"/>
-      <c r="AM10" s="69" t="s">
+      <c r="AE10" s="85"/>
+      <c r="AF10" s="86"/>
+      <c r="AG10" s="86"/>
+      <c r="AH10" s="43"/>
+      <c r="AI10" s="43"/>
+      <c r="AM10" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="AN10" s="76">
+      <c r="AN10" s="65">
         <f>SUM(AN6:AN9)</f>
-        <v>6285015.8799999999</v>
-      </c>
-      <c r="AO10" s="76">
+        <v>170814.28941176471</v>
+      </c>
+      <c r="AO10" s="65">
         <f>SUM(AO6:AO9)</f>
-        <v>3674010.34</v>
-      </c>
-      <c r="AP10" s="76">
-        <f t="shared" ref="AO10:AP10" si="1">SUM(AP6:AP9)</f>
-        <v>2312035.44</v>
-      </c>
-      <c r="AQ10" s="73"/>
-      <c r="AR10" s="68"/>
-      <c r="AU10" s="93" t="s">
+        <v>24936.721764705879</v>
+      </c>
+      <c r="AP10" s="65">
+        <f t="shared" ref="AP10" si="1">SUM(AP6:AP9)</f>
+        <v>15692.548235294113</v>
+      </c>
+      <c r="AQ10" s="62"/>
+      <c r="AR10" s="57"/>
+      <c r="AU10" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="AV10" s="95">
+      <c r="AV10" s="82">
         <f>AV9/12</f>
-        <v>115951.18785822019</v>
+        <v>1290.2512061068205</v>
       </c>
     </row>
     <row r="11" spans="1:49" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1879,53 +1897,59 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="N11" s="26" t="s">
+      <c r="N11" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="24"/>
-      <c r="P11" s="25">
+      <c r="O11" s="17"/>
+      <c r="P11" s="18">
         <v>1</v>
       </c>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="AA11" s="48" t="s">
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="12"/>
+      <c r="AA11" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="48"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="51"/>
-      <c r="AI11" s="51"/>
-      <c r="AM11" s="69" t="s">
+      <c r="AB11" s="40"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="40"/>
+      <c r="AE11" s="40"/>
+      <c r="AF11" s="40"/>
+      <c r="AG11" s="40"/>
+      <c r="AH11" s="43"/>
+      <c r="AI11" s="43"/>
+      <c r="AM11" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="AN11" s="81">
+      <c r="AN11" s="68">
         <f>(C8+C11)/C12</f>
         <v>0.13122171945701358</v>
       </c>
-      <c r="AO11" s="81">
+      <c r="AO11" s="68">
         <f>(C8+C11)/C12</f>
         <v>0.13122171945701358</v>
       </c>
-      <c r="AP11" s="81">
+      <c r="AP11" s="68">
         <f>(C8+C11)/C12</f>
         <v>0.13122171945701358</v>
       </c>
-      <c r="AQ11" s="73"/>
-      <c r="AR11" s="68"/>
-      <c r="AU11" s="93" t="s">
+      <c r="AQ11" s="62"/>
+      <c r="AR11" s="57"/>
+      <c r="AU11" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="AV11" s="95"/>
+      <c r="AV11" s="82">
+        <f>P7/AV8</f>
+        <v>390.12941046344429</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="12" spans="1:49" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1944,71 +1968,77 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-      <c r="N12" s="26" t="s">
+      <c r="N12" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="O12" s="24"/>
-      <c r="P12" s="25">
+      <c r="O12" s="17"/>
+      <c r="P12" s="18">
         <v>2</v>
       </c>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="AA12" s="45" t="s">
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="12"/>
+      <c r="AA12" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="AB12" s="49">
+      <c r="AB12" s="41">
         <f>P16</f>
         <v>7</v>
       </c>
-      <c r="AC12" s="49">
+      <c r="AC12" s="41">
         <f>P9</f>
         <v>2</v>
       </c>
-      <c r="AD12" s="50">
+      <c r="AD12" s="42">
         <f>P6*AC12</f>
         <v>6</v>
       </c>
-      <c r="AE12" s="65">
+      <c r="AE12" s="55">
         <f>C6/C12*AD12</f>
         <v>6.868778280542986</v>
       </c>
-      <c r="AF12" s="49">
+      <c r="AF12" s="41">
         <f>AE12*C12</f>
         <v>1518</v>
       </c>
-      <c r="AG12" s="49">
-        <f>AF12*AH4</f>
-        <v>1602400.7999999998</v>
-      </c>
-      <c r="AH12" s="52"/>
-      <c r="AI12" s="52"/>
-      <c r="AM12" s="69" t="s">
+      <c r="AG12" s="41">
+        <f>AF12*AH4*8</f>
+        <v>87008.188235294117</v>
+      </c>
+      <c r="AH12" s="44"/>
+      <c r="AI12" s="44"/>
+      <c r="AM12" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="AN12" s="82">
+      <c r="AN12" s="69">
         <f>AN10*AN11</f>
-        <v>824730.5905882353</v>
-      </c>
-      <c r="AO12" s="82">
+        <v>22414.544764439714</v>
+      </c>
+      <c r="AO12" s="69">
         <f>AO10*AO11</f>
-        <v>482109.95411764708</v>
-      </c>
-      <c r="AP12" s="82">
+        <v>3272.2395075858394</v>
+      </c>
+      <c r="AP12" s="69">
         <f>AP10*AP11</f>
-        <v>303389.26588235295</v>
-      </c>
-      <c r="AQ12" s="73"/>
-      <c r="AR12" s="68"/>
-      <c r="AU12" s="93" t="s">
+        <v>2059.2031620974176</v>
+      </c>
+      <c r="AQ12" s="62"/>
+      <c r="AR12" s="57"/>
+      <c r="AU12" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="AV12" s="95"/>
+      <c r="AV12" s="97">
+        <f>AV11/C12/3</f>
+        <v>0.58843048335361126</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="13" spans="1:49" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -2027,71 +2057,77 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
-      <c r="N13" s="26" t="s">
+      <c r="N13" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="O13" s="24"/>
-      <c r="P13" s="25">
+      <c r="O13" s="17"/>
+      <c r="P13" s="18">
         <v>2</v>
       </c>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="AA13" s="45" t="s">
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="AA13" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="AB13" s="49">
+      <c r="AB13" s="41">
         <f>P17</f>
         <v>3</v>
       </c>
-      <c r="AC13" s="49">
+      <c r="AC13" s="41">
         <f>P10</f>
         <v>4</v>
       </c>
-      <c r="AD13" s="50">
+      <c r="AD13" s="42">
         <f>P6*AC13</f>
         <v>12</v>
       </c>
-      <c r="AE13" s="49">
+      <c r="AE13" s="41">
         <f>C6/C12*AD13</f>
         <v>13.737556561085972</v>
       </c>
-      <c r="AF13" s="49">
+      <c r="AF13" s="41">
         <f>AE13*C12</f>
         <v>3036</v>
       </c>
-      <c r="AG13" s="49">
+      <c r="AG13" s="41">
         <f>AF13*AD4</f>
-        <v>2131272</v>
-      </c>
-      <c r="AH13" s="52"/>
-      <c r="AI13" s="52"/>
-      <c r="AM13" s="75" t="s">
+        <v>14465.64705882353</v>
+      </c>
+      <c r="AH13" s="44"/>
+      <c r="AI13" s="44"/>
+      <c r="AM13" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="AN13" s="77">
+      <c r="AN13" s="66">
         <f>AN10+AN12</f>
-        <v>7109746.4705882352</v>
-      </c>
-      <c r="AO13" s="77">
+        <v>193228.83417620443</v>
+      </c>
+      <c r="AO13" s="66">
         <f>AO10+AO12</f>
-        <v>4156120.2941176468</v>
-      </c>
-      <c r="AP13" s="77">
+        <v>28208.961272291719</v>
+      </c>
+      <c r="AP13" s="66">
         <f>AP10+AP12</f>
-        <v>2615424.7058823528</v>
-      </c>
-      <c r="AQ13" s="72"/>
-      <c r="AR13" s="72"/>
-      <c r="AU13" s="93" t="s">
+        <v>17751.75139739153</v>
+      </c>
+      <c r="AQ13" s="61"/>
+      <c r="AR13" s="61"/>
+      <c r="AU13" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="AV13" s="95"/>
+      <c r="AV13" s="98">
+        <f>AV12/8</f>
+        <v>7.3553810419201407E-2</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="14" spans="1:49" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2109,47 +2145,47 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="N14" s="23" t="s">
+      <c r="N14" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="O14" s="24"/>
-      <c r="P14" s="25">
+      <c r="O14" s="17"/>
+      <c r="P14" s="18">
         <v>1</v>
       </c>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-      <c r="AA14" s="47" t="s">
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="18"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="AA14" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="AB14" s="46"/>
-      <c r="AC14" s="57">
+      <c r="AB14" s="38"/>
+      <c r="AC14" s="49">
         <f>AC12+AC13</f>
         <v>6</v>
       </c>
-      <c r="AD14" s="57">
+      <c r="AD14" s="49">
         <f>AD12+AD13</f>
         <v>18</v>
       </c>
-      <c r="AE14" s="57">
+      <c r="AE14" s="49">
         <f>AE12+AE13</f>
         <v>20.606334841628957</v>
       </c>
-      <c r="AF14" s="57">
+      <c r="AF14" s="49">
         <f>AF12+AF13</f>
         <v>4554</v>
       </c>
-      <c r="AG14" s="57">
+      <c r="AG14" s="49">
         <f>AG12+AG13</f>
-        <v>3733672.8</v>
-      </c>
-      <c r="AH14" s="52"/>
-      <c r="AI14" s="52"/>
+        <v>101473.83529411764</v>
+      </c>
+      <c r="AH14" s="44"/>
+      <c r="AI14" s="44"/>
     </row>
     <row r="15" spans="1:49" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -2168,39 +2204,39 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
-      <c r="N15" s="29" t="s">
+      <c r="N15" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="O15" s="27"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="28"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-      <c r="AA15" s="48" t="s">
+      <c r="O15" s="20"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="AA15" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="AB15" s="48"/>
-      <c r="AC15" s="48"/>
-      <c r="AD15" s="54"/>
-      <c r="AE15" s="59"/>
-      <c r="AF15" s="59"/>
-      <c r="AG15" s="60"/>
-      <c r="AH15" s="51"/>
-      <c r="AI15" s="51"/>
-      <c r="AM15" s="37" t="s">
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="46"/>
+      <c r="AE15" s="51"/>
+      <c r="AF15" s="51"/>
+      <c r="AG15" s="52"/>
+      <c r="AH15" s="43"/>
+      <c r="AI15" s="43"/>
+      <c r="AM15" s="84" t="s">
         <v>78</v>
       </c>
-      <c r="AN15" s="37"/>
-      <c r="AO15" s="37"/>
-      <c r="AP15" s="37"/>
-      <c r="AQ15" s="37"/>
-      <c r="AR15" s="37"/>
-      <c r="AS15" s="37"/>
+      <c r="AN15" s="84"/>
+      <c r="AO15" s="84"/>
+      <c r="AP15" s="84"/>
+      <c r="AQ15" s="84"/>
+      <c r="AR15" s="84"/>
+      <c r="AS15" s="84"/>
     </row>
     <row r="16" spans="1:49" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -2219,581 +2255,595 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="N16" s="23" t="s">
+      <c r="N16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O16" s="27"/>
-      <c r="P16" s="28">
+      <c r="O16" s="20"/>
+      <c r="P16" s="21">
         <v>7</v>
       </c>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="28"/>
-      <c r="V16" s="28"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="19"/>
-      <c r="AA16" s="47" t="s">
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="AA16" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="AB16" s="49">
+      <c r="AB16" s="41">
         <f>P18</f>
         <v>5</v>
       </c>
-      <c r="AC16" s="49">
+      <c r="AC16" s="41">
         <f>P11</f>
         <v>1</v>
       </c>
-      <c r="AD16" s="50">
+      <c r="AD16" s="42">
         <f>AC16*P6</f>
         <v>3</v>
       </c>
-      <c r="AE16" s="49">
+      <c r="AE16" s="41">
         <f>$C$6/$C$12*AD16</f>
         <v>3.434389140271493</v>
       </c>
-      <c r="AF16" s="49">
+      <c r="AF16" s="41">
         <f>AE16*$C$12</f>
         <v>759</v>
       </c>
-      <c r="AG16" s="56">
+      <c r="AG16" s="48">
         <f>AF16*AF4</f>
-        <v>682796.4</v>
-      </c>
-      <c r="AH16" s="52"/>
-      <c r="AI16" s="53"/>
-      <c r="AM16" s="84" t="s">
+        <v>4634.3647058823526</v>
+      </c>
+      <c r="AH16" s="44"/>
+      <c r="AI16" s="45"/>
+      <c r="AM16" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="AN16" s="64" t="s">
+      <c r="AN16" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="AO16" s="63" t="s">
+      <c r="AO16" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="AP16" s="12" t="s">
+      <c r="AP16" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="AQ16" s="13"/>
-      <c r="AR16" s="13"/>
-      <c r="AS16" s="14"/>
+      <c r="AQ16" s="88"/>
+      <c r="AR16" s="88"/>
+      <c r="AS16" s="89"/>
     </row>
     <row r="17" spans="14:45" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="N17" s="23" t="s">
+      <c r="N17" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="O17" s="27"/>
-      <c r="P17" s="28">
+      <c r="O17" s="20"/>
+      <c r="P17" s="21">
         <v>3</v>
       </c>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28"/>
-      <c r="T17" s="28"/>
-      <c r="U17" s="28"/>
-      <c r="V17" s="28"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-      <c r="AA17" s="47" t="s">
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="AA17" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="AB17" s="49">
+      <c r="AB17" s="41">
         <f>P19</f>
         <v>6</v>
       </c>
-      <c r="AC17" s="49">
+      <c r="AC17" s="41">
         <f>P12</f>
         <v>2</v>
       </c>
-      <c r="AD17" s="50">
+      <c r="AD17" s="42">
         <f>AC17*P6</f>
         <v>6</v>
       </c>
-      <c r="AE17" s="49">
+      <c r="AE17" s="41">
         <f t="shared" ref="AE17" si="2">$C$6/$C$12*AD17</f>
         <v>6.868778280542986</v>
       </c>
-      <c r="AF17" s="49">
+      <c r="AF17" s="41">
         <f t="shared" ref="AF17:AF18" si="3">AE17*$C$12</f>
         <v>1518</v>
       </c>
-      <c r="AG17" s="56">
+      <c r="AG17" s="48">
         <f>AF17*AG4</f>
-        <v>1499784</v>
-      </c>
-      <c r="AH17" s="52"/>
-      <c r="AI17" s="52"/>
-      <c r="AM17" s="84"/>
-      <c r="AN17" s="64"/>
-      <c r="AO17" s="63"/>
-      <c r="AP17" s="84" t="s">
+        <v>10179.529411764704</v>
+      </c>
+      <c r="AH17" s="44"/>
+      <c r="AI17" s="44"/>
+      <c r="AM17" s="71"/>
+      <c r="AN17" s="85"/>
+      <c r="AO17" s="86"/>
+      <c r="AP17" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="AQ17" s="84" t="s">
+      <c r="AQ17" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="AR17" s="84" t="s">
+      <c r="AR17" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="AS17" s="84" t="s">
+      <c r="AS17" s="71" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="18" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N18" s="26" t="s">
+      <c r="N18" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="O18" s="27"/>
-      <c r="P18" s="28">
+      <c r="O18" s="20"/>
+      <c r="P18" s="21">
         <v>5</v>
       </c>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
-      <c r="V18" s="28"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="AA18" s="47" t="s">
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="AA18" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="AB18" s="59"/>
-      <c r="AC18" s="58">
+      <c r="AB18" s="51"/>
+      <c r="AC18" s="50">
         <f>AC16+AC17</f>
         <v>3</v>
       </c>
-      <c r="AD18" s="58">
+      <c r="AD18" s="50">
         <f>AC18*P6</f>
         <v>9</v>
       </c>
-      <c r="AE18" s="49">
+      <c r="AE18" s="41">
         <f>$C$6/$C$12*AD18</f>
         <v>10.303167420814479</v>
       </c>
-      <c r="AF18" s="49">
+      <c r="AF18" s="41">
         <f t="shared" si="3"/>
         <v>2276.9999999999995</v>
       </c>
-      <c r="AG18" s="58">
+      <c r="AG18" s="50">
         <f>AG16+AG17</f>
-        <v>2182580.4</v>
-      </c>
-      <c r="AH18" s="52"/>
-      <c r="AI18" s="52"/>
-      <c r="AM18" s="89" t="s">
+        <v>14813.894117647058</v>
+      </c>
+      <c r="AH18" s="44"/>
+      <c r="AI18" s="44"/>
+      <c r="AM18" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="AN18" s="86">
+      <c r="AN18" s="73">
         <f>P23</f>
         <v>2</v>
       </c>
-      <c r="AO18" s="86">
+      <c r="AO18" s="73">
         <f>P27</f>
         <v>3100</v>
       </c>
-      <c r="AP18" s="85">
-        <f>AO18*AN18</f>
-        <v>6200</v>
-      </c>
-      <c r="AQ18" s="86">
+      <c r="AP18" s="72">
+        <f>AO18*AN18*12</f>
+        <v>74400</v>
+      </c>
+      <c r="AQ18" s="73">
         <f>AP18*$P$5/100</f>
-        <v>3410</v>
-      </c>
-      <c r="AR18" s="86">
+        <v>40920</v>
+      </c>
+      <c r="AR18" s="73">
         <f>AP18*AN11</f>
-        <v>813.5746606334842</v>
-      </c>
-      <c r="AS18" s="86">
+        <v>9762.8959276018104</v>
+      </c>
+      <c r="AS18" s="73">
         <f>SUM(AP18:AR18)</f>
-        <v>10423.574660633483</v>
+        <v>125082.89592760181</v>
       </c>
     </row>
     <row r="19" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N19" s="26" t="s">
+      <c r="N19" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="O19" s="27"/>
-      <c r="P19" s="28">
+      <c r="O19" s="20"/>
+      <c r="P19" s="21">
         <v>6</v>
       </c>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="AA19" s="48" t="s">
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="AA19" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="54"/>
-      <c r="AE19" s="59"/>
-      <c r="AF19" s="59"/>
-      <c r="AG19" s="55"/>
-      <c r="AH19" s="51"/>
-      <c r="AI19" s="51"/>
-      <c r="AM19" s="83" t="s">
+      <c r="AB19" s="40"/>
+      <c r="AC19" s="40"/>
+      <c r="AD19" s="46"/>
+      <c r="AE19" s="51"/>
+      <c r="AF19" s="51"/>
+      <c r="AG19" s="47"/>
+      <c r="AH19" s="43"/>
+      <c r="AI19" s="43"/>
+      <c r="AM19" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="AN19" s="86">
+      <c r="AN19" s="73">
         <f>P24</f>
         <v>2</v>
       </c>
-      <c r="AO19" s="86">
+      <c r="AO19" s="73">
         <f>P28</f>
         <v>2800</v>
       </c>
-      <c r="AP19" s="85">
-        <f>AO19*AN19</f>
-        <v>5600</v>
-      </c>
-      <c r="AQ19" s="86">
+      <c r="AP19" s="72">
+        <f>AO19*AN19*12</f>
+        <v>67200</v>
+      </c>
+      <c r="AQ19" s="73">
         <f t="shared" ref="AQ19:AQ20" si="4">AP19*$P$5/100</f>
-        <v>3080</v>
-      </c>
-      <c r="AR19" s="86">
+        <v>36960</v>
+      </c>
+      <c r="AR19" s="73">
         <f>AP19*AN11</f>
-        <v>734.84162895927602</v>
-      </c>
-      <c r="AS19" s="86">
-        <f t="shared" ref="AS19:AS20" si="5">SUM(AP19:AR19)</f>
-        <v>9414.8416289592751</v>
+        <v>8818.0995475113123</v>
+      </c>
+      <c r="AS19" s="73">
+        <f t="shared" ref="AS19" si="5">SUM(AP19:AR19)</f>
+        <v>112978.09954751132</v>
       </c>
     </row>
     <row r="20" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N20" s="26" t="s">
+      <c r="N20" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="O20" s="27"/>
-      <c r="P20" s="28">
+      <c r="O20" s="20"/>
+      <c r="P20" s="21">
         <v>2</v>
       </c>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="19"/>
-      <c r="AA20" s="47" t="s">
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="AA20" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="AB20" s="49">
+      <c r="AB20" s="41">
         <f>P20</f>
         <v>2</v>
       </c>
-      <c r="AC20" s="49">
+      <c r="AC20" s="41">
         <f>P13</f>
         <v>2</v>
       </c>
-      <c r="AD20" s="50">
+      <c r="AD20" s="42">
         <f>AC20*P6</f>
         <v>6</v>
       </c>
-      <c r="AE20" s="49">
+      <c r="AE20" s="41">
         <f>$C$6/$C$12*AD20</f>
         <v>6.868778280542986</v>
       </c>
-      <c r="AF20" s="49">
+      <c r="AF20" s="41">
         <f>AE20*$C$12</f>
         <v>1518</v>
       </c>
-      <c r="AG20" s="56">
+      <c r="AG20" s="48">
         <f>AF20*AC4</f>
-        <v>915657.59999999986</v>
-      </c>
-      <c r="AH20" s="52"/>
-      <c r="AI20" s="52"/>
-      <c r="AM20" s="83" t="s">
+        <v>6214.8705882352933</v>
+      </c>
+      <c r="AH20" s="44"/>
+      <c r="AI20" s="44"/>
+      <c r="AM20" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="AN20" s="86">
+      <c r="AN20" s="73">
         <f>P25</f>
         <v>3</v>
       </c>
-      <c r="AO20" s="86">
+      <c r="AO20" s="73">
         <f>P29</f>
         <v>2580</v>
       </c>
-      <c r="AP20" s="85">
-        <f>AO20*AN20</f>
-        <v>7740</v>
-      </c>
-      <c r="AQ20" s="86">
+      <c r="AP20" s="72">
+        <f>AO20*AN20*12</f>
+        <v>92880</v>
+      </c>
+      <c r="AQ20" s="73">
         <f t="shared" si="4"/>
-        <v>4257</v>
-      </c>
-      <c r="AR20" s="86">
+        <v>51084</v>
+      </c>
+      <c r="AR20" s="73">
         <f>AP20*AP11</f>
-        <v>1015.6561085972851</v>
-      </c>
-      <c r="AS20" s="86">
+        <v>12187.873303167422</v>
+      </c>
+      <c r="AS20" s="73">
         <f>SUM(AP20:AR20)</f>
-        <v>13012.656108597284</v>
+        <v>156151.87330316743</v>
       </c>
     </row>
     <row r="21" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N21" s="23" t="s">
+      <c r="N21" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="O21" s="27"/>
-      <c r="P21" s="28">
+      <c r="O21" s="20"/>
+      <c r="P21" s="21">
         <v>2</v>
       </c>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="28"/>
-      <c r="U21" s="28"/>
-      <c r="V21" s="28"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="19"/>
-      <c r="AA21" s="47" t="s">
+      <c r="Q21" s="21"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="21"/>
+      <c r="V21" s="21"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="AA21" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="AB21" s="49">
+      <c r="AB21" s="41">
         <f>P21</f>
         <v>2</v>
       </c>
-      <c r="AC21" s="49">
+      <c r="AC21" s="41">
         <f>P14</f>
         <v>1</v>
       </c>
-      <c r="AD21" s="50">
+      <c r="AD21" s="42">
         <f>AC21*P6</f>
         <v>3</v>
       </c>
-      <c r="AE21" s="49">
+      <c r="AE21" s="41">
         <f t="shared" ref="AE21" si="6">$C$6/$C$12*AD21</f>
         <v>3.434389140271493</v>
       </c>
-      <c r="AF21" s="49">
+      <c r="AF21" s="41">
         <f t="shared" ref="AF21:AF22" si="7">AE21*$C$12</f>
         <v>759</v>
       </c>
-      <c r="AG21" s="56">
+      <c r="AG21" s="48">
         <f>AF21*AC4</f>
-        <v>457828.79999999993</v>
-      </c>
-      <c r="AH21" s="52"/>
-      <c r="AI21" s="52"/>
-      <c r="AM21" s="83" t="s">
+        <v>3107.4352941176467</v>
+      </c>
+      <c r="AH21" s="44"/>
+      <c r="AI21" s="44"/>
+      <c r="AM21" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="AN21" s="88">
+      <c r="AN21" s="75">
         <f>AN18+AN19+AN20</f>
         <v>7</v>
       </c>
-      <c r="AO21" s="87"/>
-      <c r="AP21" s="88">
+      <c r="AO21" s="74"/>
+      <c r="AP21" s="75">
         <f>SUM(AP18:AP20)</f>
-        <v>19540</v>
-      </c>
-      <c r="AQ21" s="88">
+        <v>234480</v>
+      </c>
+      <c r="AQ21" s="75">
         <f>SUM(AQ18:AQ20)</f>
-        <v>10747</v>
-      </c>
-      <c r="AR21" s="88">
+        <v>128964</v>
+      </c>
+      <c r="AR21" s="75">
         <f>SUM(AR18:AR20)</f>
-        <v>2564.0723981900455</v>
-      </c>
-      <c r="AS21" s="88">
+        <v>30768.868778280543</v>
+      </c>
+      <c r="AS21" s="75">
         <f>SUM(AS18:AS20)</f>
-        <v>32851.072398190045</v>
+        <v>394212.86877828056</v>
       </c>
     </row>
     <row r="22" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N22" s="30" t="s">
+      <c r="N22" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="O22" s="24"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-      <c r="AA22" s="47" t="s">
+      <c r="O22" s="17"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="AA22" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="AB22" s="46"/>
-      <c r="AC22" s="57">
+      <c r="AB22" s="38"/>
+      <c r="AC22" s="49">
         <f>AC21+AC20</f>
         <v>3</v>
       </c>
-      <c r="AD22" s="57">
+      <c r="AD22" s="49">
         <f>AC22*P6</f>
         <v>9</v>
       </c>
-      <c r="AE22" s="49">
+      <c r="AE22" s="41">
         <f>AE20+AE21</f>
         <v>10.303167420814479</v>
       </c>
-      <c r="AF22" s="49">
+      <c r="AF22" s="41">
         <f t="shared" si="7"/>
         <v>2276.9999999999995</v>
       </c>
-      <c r="AG22" s="58">
+      <c r="AG22" s="50">
         <f>AG20+AG21</f>
-        <v>1373486.4</v>
-      </c>
-      <c r="AH22" s="52"/>
-      <c r="AI22" s="52"/>
+        <v>9322.3058823529391</v>
+      </c>
+      <c r="AH22" s="44"/>
+      <c r="AI22" s="44"/>
     </row>
     <row r="23" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N23" s="26" t="s">
+      <c r="N23" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="O23" s="24"/>
-      <c r="P23" s="25">
+      <c r="O23" s="17"/>
+      <c r="P23" s="18">
         <v>2</v>
       </c>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="19"/>
-      <c r="X23" s="19"/>
-      <c r="AA23" s="47" t="s">
+      <c r="Q23" s="18"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="AA23" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="AB23" s="46"/>
-      <c r="AC23" s="61">
+      <c r="AB23" s="38"/>
+      <c r="AC23" s="53">
         <f>AC14+AC22</f>
         <v>9</v>
       </c>
-      <c r="AD23" s="61">
+      <c r="AD23" s="53">
         <f>AD22+AD14</f>
         <v>27</v>
       </c>
-      <c r="AE23" s="61">
+      <c r="AE23" s="53">
         <f>AE22+AE14</f>
         <v>30.909502262443436</v>
       </c>
-      <c r="AF23" s="61">
+      <c r="AF23" s="53">
         <f>AF14+AF22</f>
         <v>6831</v>
       </c>
-      <c r="AG23" s="61">
+      <c r="AG23" s="53">
         <f>AG14+AG22</f>
-        <v>5107159.1999999993</v>
-      </c>
-      <c r="AH23" s="52"/>
-      <c r="AI23" s="52"/>
+        <v>110796.14117647058</v>
+      </c>
+      <c r="AH23" s="44"/>
+      <c r="AI23" s="44"/>
     </row>
     <row r="24" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N24" s="26" t="s">
+      <c r="N24" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="O24" s="24"/>
-      <c r="P24" s="25">
+      <c r="O24" s="17"/>
+      <c r="P24" s="18">
         <v>2</v>
       </c>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="25"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
     </row>
     <row r="25" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N25" s="26" t="s">
+      <c r="N25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="O25" s="24"/>
-      <c r="P25" s="25">
+      <c r="O25" s="17"/>
+      <c r="P25" s="18">
         <v>3</v>
       </c>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="25"/>
-      <c r="S25" s="25"/>
-      <c r="T25" s="25"/>
-      <c r="U25" s="25"/>
-      <c r="V25" s="25"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="12"/>
+      <c r="X25" s="12"/>
     </row>
     <row r="26" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N26" s="31" t="s">
+      <c r="N26" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="O26" s="24"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25"/>
-      <c r="T26" s="25"/>
-      <c r="U26" s="25"/>
-      <c r="V26" s="25"/>
-      <c r="W26" s="19"/>
-      <c r="X26" s="19"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
     </row>
     <row r="27" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N27" s="26" t="s">
+      <c r="N27" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="O27" s="24"/>
-      <c r="P27" s="25">
+      <c r="O27" s="17"/>
+      <c r="P27" s="18">
         <v>3100</v>
       </c>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="25"/>
-      <c r="T27" s="25"/>
-      <c r="U27" s="25"/>
-      <c r="V27" s="25"/>
-      <c r="W27" s="19"/>
-      <c r="X27" s="19"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
     </row>
     <row r="28" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N28" s="26" t="s">
+      <c r="N28" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="O28" s="24"/>
-      <c r="P28" s="25">
+      <c r="O28" s="17"/>
+      <c r="P28" s="18">
         <v>2800</v>
       </c>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="25"/>
-      <c r="S28" s="25"/>
-      <c r="T28" s="25"/>
-      <c r="U28" s="25"/>
-      <c r="V28" s="25"/>
-      <c r="W28" s="19"/>
-      <c r="X28" s="19"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
     </row>
     <row r="29" spans="14:45" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="N29" s="26" t="s">
+      <c r="N29" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="O29" s="24"/>
-      <c r="P29" s="25">
+      <c r="O29" s="17"/>
+      <c r="P29" s="18">
         <v>2580</v>
       </c>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="25"/>
-      <c r="S29" s="25"/>
-      <c r="T29" s="25"/>
-      <c r="U29" s="25"/>
-      <c r="V29" s="25"/>
-      <c r="W29" s="19"/>
-      <c r="X29" s="19"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="N1:U1"/>
+    <mergeCell ref="O2:X2"/>
+    <mergeCell ref="AA2:AH2"/>
+    <mergeCell ref="AA7:AI7"/>
+    <mergeCell ref="AB8:AE8"/>
+    <mergeCell ref="AF8:AG8"/>
+    <mergeCell ref="AA8:AA10"/>
+    <mergeCell ref="AB9:AB10"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="AE9:AE10"/>
+    <mergeCell ref="AF9:AF10"/>
+    <mergeCell ref="AG9:AG10"/>
     <mergeCell ref="AM15:AS15"/>
     <mergeCell ref="AN16:AN17"/>
     <mergeCell ref="AO16:AO17"/>
@@ -2803,20 +2853,6 @@
     <mergeCell ref="AR8:AR9"/>
     <mergeCell ref="AM4:AM5"/>
     <mergeCell ref="AN4:AP4"/>
-    <mergeCell ref="AA7:AI7"/>
-    <mergeCell ref="AB8:AE8"/>
-    <mergeCell ref="AF8:AG8"/>
-    <mergeCell ref="AA8:AA10"/>
-    <mergeCell ref="AB9:AB10"/>
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="AE9:AE10"/>
-    <mergeCell ref="AF9:AF10"/>
-    <mergeCell ref="AG9:AG10"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="N1:U1"/>
-    <mergeCell ref="O2:X2"/>
-    <mergeCell ref="AA2:AH2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
